--- a/Диаграммы.xlsx
+++ b/Диаграммы.xlsx
@@ -8,26 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arko/Documents/GitHub/university-projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{896E2BAB-E134-D640-A2C8-DDD458AB1161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EEBD80-5EFA-6C49-82B7-21217DEF6D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="580" yWindow="760" windowWidth="28240" windowHeight="17140" xr2:uid="{FE6CC1D7-2279-F44F-B80F-E825FECDE41E}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{FE6CC1D7-2279-F44F-B80F-E825FECDE41E}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v2.0" hidden="1">Лист1!$A$7:$A$10</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Лист1!$B$7:$B$10</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Лист1!$A$44:$A$47</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Лист1!$B$44:$B$47</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">Лист1!$A$29:$A$32</definedName>
-    <definedName name="_xlchart.v2.5" hidden="1">Лист1!$B$29:$B$32</definedName>
-    <definedName name="_xlchart.v2.6" hidden="1">Лист1!$A$58:$A$61</definedName>
-    <definedName name="_xlchart.v2.7" hidden="1">Лист1!$B$58:$B$61</definedName>
-    <definedName name="_xlchart.v2.8" hidden="1">Лист1!$A$58:$A$61</definedName>
-    <definedName name="_xlchart.v2.9" hidden="1">Лист1!$B$58:$B$61</definedName>
+    <definedName name="_xlchart.v2.0" hidden="1">Лист1!$A$18:$A$21</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">Лист1!$B$18:$B$21</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">Лист1!$C$18:$C$21</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">Лист1!$A$34:$A$37</definedName>
+    <definedName name="_xlchart.v2.4" hidden="1">Лист1!$B$34:$B$37</definedName>
+    <definedName name="_xlchart.v2.5" hidden="1">Лист1!$C$34:$C$37</definedName>
+    <definedName name="_xlchart.v2.6" hidden="1">Лист1!$A$34:$A$37</definedName>
+    <definedName name="_xlchart.v2.7" hidden="1">Лист1!$B$34:$B$37</definedName>
+    <definedName name="_xlchart.v2.8" hidden="1">Лист1!$C$34:$C$37</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,48 +47,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Case Keys (Ключи от кейсов)</t>
-  </si>
-  <si>
-    <t>Steam Market Fee (Комиссия ТП)</t>
-  </si>
-  <si>
-    <t>Prime Status Upgrade</t>
-  </si>
-  <si>
-    <t>Operation Passes/Capsules</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>App Start</t>
   </si>
   <si>
-    <t>Tutorial Start</t>
+    <t>Prime Status</t>
   </si>
   <si>
-    <t>First Deathmatch</t>
+    <t>Case Keys</t>
   </si>
   <si>
-    <t xml:space="preserve">First Premier Match </t>
+    <t>App Start 100% (49752) -&gt; Tutorial Complete 90,1% (44806) -&gt; Deathmatch 53,9% (26814) -&gt; Premier Match 3,0% (1476</t>
   </si>
   <si>
-    <t xml:space="preserve">Case Drop </t>
+    <t>Deathmatch</t>
   </si>
   <si>
-    <t xml:space="preserve">Inspect Case </t>
+    <t>Tutorial Complete</t>
   </si>
   <si>
-    <t xml:space="preserve">Click "Buy Key" </t>
+    <t>Premier Match</t>
   </si>
   <si>
-    <t xml:space="preserve">Payment Success </t>
+    <t>Case Drop 100% (27779) -&gt; Inspect 61,8% (17173) -&gt; Click Buy 4,6% (1285) -&gt; Payment Success 4,3% (1204)</t>
+  </si>
+  <si>
+    <t>Case Drop</t>
+  </si>
+  <si>
+    <t>Inspect</t>
+  </si>
+  <si>
+    <t>Click Buy</t>
+  </si>
+  <si>
+    <t>Payment Success</t>
+  </si>
+  <si>
+    <t>Search Started 100% (918108) -&gt; Match Found 95% (872202) -&gt; Match Started 94,9% (871647) -&gt; Match Finished 71,2% (653581)</t>
   </si>
   <si>
     <t>Search Started</t>
   </si>
   <si>
-    <t>Match Accepted</t>
+    <t>Match Found</t>
   </si>
   <si>
     <t>Match Started</t>
@@ -96,24 +99,15 @@
   <si>
     <t>Match Finished</t>
   </si>
-  <si>
-    <t>News Impression</t>
-  </si>
-  <si>
-    <t>Library Click</t>
-  </si>
-  <si>
-    <t>Update Start</t>
-  </si>
-  <si>
-    <t>Game Login</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -133,6 +127,13 @@
       <i/>
       <sz val="14"/>
       <color rgb="FFE2E2E5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -157,12 +158,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -214,8 +218,16 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Распределение выручки</a:t>
+              <a:rPr lang="ru-RU" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Структура выручки </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>CS2</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -275,6 +287,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-13D2-4841-9922-CAE74EE6CD88}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -290,6 +307,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-13D2-4841-9922-CAE74EE6CD88}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -305,6 +327,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-13D2-4841-9922-CAE74EE6CD88}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -320,23 +347,22 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-13D2-4841-9922-CAE74EE6CD88}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
               <c:f>Лист1!$A$1:$A$4</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Case Keys (Ключи от кейсов)</c:v>
+                  <c:v>Prime Status</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Steam Market Fee (Комиссия ТП)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Prime Status Upgrade</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Operation Passes/Capsules</c:v>
+                  <c:v>Case Keys</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -345,19 +371,13 @@
             <c:numRef>
               <c:f>Лист1!$B$1:$B$4</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.65</c:v>
+                  <c:v>0.92200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>7.8E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -389,6 +409,14 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -473,23 +501,41 @@
         <cx:f>_xlchart.v2.1</cx:f>
       </cx:numDim>
     </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v2.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v2.2</cx:f>
+      </cx:numDim>
+    </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
-        <cx:txData>
-          <cx:v>Воронка анбординга</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Воронка анбординга</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -497,22 +543,27 @@
                 </a:sysClr>
               </a:solidFill>
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Воронка анбординга</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
+            </a:endParaRPr>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{B161D2E2-F905-2D41-B969-8C5EEEA82576}">
+        <cx:series layoutId="funnel" uniqueId="{884CD445-18B6-1F4D-A598-1EE75EEC8981}" formatIdx="0">
           <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
         </cx:series>
+        <cx:series layoutId="funnel" hidden="1" uniqueId="{8B3C999D-D401-FA45-AD42-1D216A240021}" formatIdx="1">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="1"/>
+        </cx:series>
       </cx:plotAreaRegion>
-      <cx:axis id="1">
+      <cx:axis id="0">
         <cx:catScaling gapWidth="0.0599999987"/>
         <cx:tickLabels/>
       </cx:axis>
@@ -526,7 +577,15 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
+        <cx:f>_xlchart.v2.3</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
         <cx:f>_xlchart.v2.4</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v2.3</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
         <cx:f>_xlchart.v2.5</cx:f>
@@ -536,19 +595,29 @@
   <cx:chart>
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
-        <cx:txData>
-          <cx:v>Воронка "Кейс - ключ"</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Кейс – ключ</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
@@ -556,137 +625,24 @@
                 </a:sysClr>
               </a:solidFill>
               <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Воронка "Кейс - ключ"</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
+            </a:endParaRPr>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{BE9D1559-2B1D-3842-B43D-22099A9DA364}">
+        <cx:series layoutId="funnel" uniqueId="{2D28DCCA-122B-964C-9495-A62BFBF85EFF}" formatIdx="0">
           <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
         </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="1">
-        <cx:catScaling gapWidth="0.0599999987"/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
-<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.2</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v2.3</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Завершение матча</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Завершение матча</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{662EBBC7-F065-4844-A4C8-10EC504A841C}">
+        <cx:series layoutId="funnel" hidden="1" uniqueId="{E346E711-6021-6944-8572-FF1EA4362675}" formatIdx="1">
           <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
-          <cx:dataId val="0"/>
-        </cx:series>
-      </cx:plotAreaRegion>
-      <cx:axis id="1">
-        <cx:catScaling gapWidth="0.0599999987"/>
-        <cx:tickLabels/>
-      </cx:axis>
-    </cx:plotArea>
-  </cx:chart>
-</cx:chartSpace>
-</file>
-
-<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
-<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
-  <cx:chartData>
-    <cx:data id="0">
-      <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.8</cx:f>
-      </cx:strDim>
-      <cx:numDim type="val">
-        <cx:f>_xlchart.v2.9</cx:f>
-      </cx:numDim>
-    </cx:data>
-  </cx:chartData>
-  <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Реактивация игроков после обновления</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Реактивация игроков после обновления</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
-    <cx:plotArea>
-      <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{E441ED80-3118-B742-80D1-58A5ACB9E38E}">
-          <cx:dataLabels>
-            <cx:visibility seriesName="0" categoryName="0" value="1"/>
-          </cx:dataLabels>
-          <cx:dataId val="0"/>
+          <cx:dataId val="1"/>
         </cx:series>
       </cx:plotAreaRegion>
       <cx:axis id="1">
@@ -818,86 +774,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
@@ -2433,1036 +2309,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat">
-        <a:solidFill>
-          <a:srgbClr val="D9D9D9"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>91017</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>33867</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3489,25 +2349,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1833463</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>31026</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>102358</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>50042</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>529704</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>161884</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>551596</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>148988</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="4" name="Диаграмма 3">
+            <xdr:cNvPr id="3" name="Диаграмма 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F81DFCC5-8FD1-E9C5-CC88-5CD7E1394B36}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84473D9E-EE42-1A02-3371-697CA4B33DB3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3534,8 +2394,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1833463" y="2635330"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="4318758" y="3733042"/>
+              <a:ext cx="4576738" cy="2791346"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3567,25 +2427,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>287866</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>42334</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>711199</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>8467</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="Диаграмма 4">
+            <xdr:cNvPr id="4" name="Диаграмма 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4252C84F-9097-0C0D-6CAB-7CCF50C22876}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E812CFB-5341-5E6C-9F10-04690A12F78B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3612,163 +2472,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3691466" y="6002867"/>
-              <a:ext cx="4572000" cy="2743200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100"/>
-                <a:t>Эта диаграмма недоступна в вашей версии Excel.
-Изменение этой фигуры или сохранение книги в другом формате приведет к остаточному повреждению диаграммы.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>198088</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>6230</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>656566</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>25719</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Диаграмма 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F58639A3-C67B-A056-81A1-2038F9E93FC4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3584755" y="8976104"/>
-              <a:ext cx="4572000" cy="2743200"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="ru-RU" sz="1100"/>
-                <a:t>Эта диаграмма недоступна в вашей версии Excel.
-Изменение этой фигуры или сохранение книги в другом формате приведет к остаточному повреждению диаграммы.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="7" name="Диаграмма 6">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A585633-1AE3-1FB2-3F2A-7FF62EC31C84}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="3568700" y="12001500"/>
+              <a:off x="4337050" y="7099300"/>
               <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4099,171 +2803,247 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F735507E-280A-8740-92C0-6C8C7D35D073}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5">
+        <v>7.8E-2</v>
+      </c>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
+      <c r="B10" s="2"/>
+    </row>
+    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="B17" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B18" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="C18">
+        <v>49752</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="C19">
+        <v>44806</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B20" s="6">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="C20">
+        <v>26814</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="C21">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A30" s="4"/>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A31" s="4"/>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A32" s="4"/>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="B33" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="2">
+      <c r="C34">
+        <v>27779</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="C35">
+        <v>17173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="6">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="C36">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="6">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="C37">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A44" s="4"/>
+      <c r="B44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A46" s="4"/>
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A47" s="4"/>
+      <c r="B47" s="2"/>
+    </row>
+    <row r="50" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="B50" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B51" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="2">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="2">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="2">
+      <c r="C51">
+        <v>918108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="2">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+      <c r="C52">
+        <v>872202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="2">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
+      <c r="B53" s="6">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="C53">
+        <v>871647</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>16</v>
       </c>
-      <c r="B58" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B59" s="2">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B60" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="18" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B61" s="2">
-        <v>0.12</v>
-      </c>
+      <c r="B54" s="6">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="C54">
+        <v>653581</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A58" s="4"/>
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A59" s="4"/>
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A60" s="4"/>
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A61" s="4"/>
+      <c r="B61" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Диаграммы.xlsx
+++ b/Диаграммы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arko/Documents/GitHub/university-projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EEBD80-5EFA-6C49-82B7-21217DEF6D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A373C770-4F25-4147-B863-0F10BF57E91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{FE6CC1D7-2279-F44F-B80F-E825FECDE41E}"/>
   </bookViews>
@@ -16,18 +16,20 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v2.0" hidden="1">Лист1!$A$18:$A$21</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Лист1!$B$18:$B$21</definedName>
-    <definedName name="_xlchart.v2.2" hidden="1">Лист1!$C$18:$C$21</definedName>
-    <definedName name="_xlchart.v2.3" hidden="1">Лист1!$A$34:$A$37</definedName>
-    <definedName name="_xlchart.v2.4" hidden="1">Лист1!$B$34:$B$37</definedName>
-    <definedName name="_xlchart.v2.5" hidden="1">Лист1!$C$34:$C$37</definedName>
+    <definedName name="_xlchart.v2.0" hidden="1">Лист1!$A$51:$A$54</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">Лист1!$B$51:$B$54</definedName>
+    <definedName name="_xlchart.v2.10" hidden="1">Лист1!$B$18:$B$21</definedName>
+    <definedName name="_xlchart.v2.11" hidden="1">Лист1!$C$18:$C$21</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">Лист1!$C$51:$C$54</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">Лист1!$A$51:$A$54</definedName>
+    <definedName name="_xlchart.v2.4" hidden="1">Лист1!$B$51:$B$54</definedName>
+    <definedName name="_xlchart.v2.5" hidden="1">Лист1!$C$51:$C$54</definedName>
     <definedName name="_xlchart.v2.6" hidden="1">Лист1!$A$34:$A$37</definedName>
     <definedName name="_xlchart.v2.7" hidden="1">Лист1!$B$34:$B$37</definedName>
     <definedName name="_xlchart.v2.8" hidden="1">Лист1!$C$34:$C$37</definedName>
+    <definedName name="_xlchart.v2.9" hidden="1">Лист1!$A$18:$A$21</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -495,18 +497,18 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.0</cx:f>
+        <cx:f>_xlchart.v2.9</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.1</cx:f>
+        <cx:f>_xlchart.v2.10</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.0</cx:f>
+        <cx:f>_xlchart.v2.9</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.2</cx:f>
+        <cx:f>_xlchart.v2.11</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -577,18 +579,18 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.3</cx:f>
+        <cx:f>_xlchart.v2.6</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.4</cx:f>
+        <cx:f>_xlchart.v2.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v2.3</cx:f>
+        <cx:f>_xlchart.v2.6</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.5</cx:f>
+        <cx:f>_xlchart.v2.8</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -639,6 +641,88 @@
           <cx:dataId val="0"/>
         </cx:series>
         <cx:series layoutId="funnel" hidden="1" uniqueId="{E346E711-6021-6944-8572-FF1EA4362675}" formatIdx="1">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="1"/>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0.0599999987"/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v2.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v2.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v2.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v2.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Завершение матча</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:rich>
+      </cx:tx>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="funnel" uniqueId="{FA0B7694-D7C3-5944-AD58-67B0DBB65949}" formatIdx="0">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+        </cx:series>
+        <cx:series layoutId="funnel" hidden="1" uniqueId="{BDF46189-BEC2-1843-B1AB-77DD0819B253}" formatIdx="1">
           <cx:dataLabels>
             <cx:visibility seriesName="0" categoryName="0" value="1"/>
           </cx:dataLabels>
@@ -774,6 +858,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
@@ -1802,6 +1926,514 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2503,6 +3135,84 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Диаграмма 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F72096B-4095-899C-0900-EE162B625AC2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4311650" y="10718800"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="ru-RU" sz="1100"/>
+                <a:t>Эта диаграмма недоступна в вашей версии Excel.
+Изменение этой фигуры или сохранение книги в другом формате приведет к остаточному повреждению диаграммы.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
